--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1655411288271</v>
+        <v>1.814400433434404</v>
       </c>
       <c r="D2" t="n">
-        <v>12.11908888377309</v>
+        <v>1.969351943613127</v>
       </c>
       <c r="E2" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F2" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.02373079832745</v>
+        <v>8.128856254728211</v>
       </c>
       <c r="D3" t="n">
-        <v>37.19763395880793</v>
+        <v>6.044615518306288</v>
       </c>
       <c r="E3" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F3" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.63827726640057</v>
+        <v>5.953720055790093</v>
       </c>
       <c r="D4" t="n">
-        <v>12.96040735400305</v>
+        <v>2.106066195025496</v>
       </c>
       <c r="E4" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F4" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.96746742973786</v>
+        <v>7.794713457332402</v>
       </c>
       <c r="D5" t="n">
-        <v>18.1062476098228</v>
+        <v>2.942265236596205</v>
       </c>
       <c r="E5" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F5" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.08666563916157</v>
+        <v>10.90158316636376</v>
       </c>
       <c r="D6" t="n">
-        <v>39.65955648006277</v>
+        <v>6.4446779280102</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F6" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.700222941693</v>
+        <v>5.801286228025113</v>
       </c>
       <c r="D7" t="n">
-        <v>18.21515810585072</v>
+        <v>2.959963192200742</v>
       </c>
       <c r="E7" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F7" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.49452026846527</v>
+        <v>9.667859543625607</v>
       </c>
       <c r="D8" t="n">
-        <v>36.54229181630898</v>
+        <v>5.93812242015021</v>
       </c>
       <c r="E8" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F8" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.22159124587639</v>
+        <v>3.448508577454914</v>
       </c>
       <c r="D9" t="n">
-        <v>21.30792525150701</v>
+        <v>3.462537853369889</v>
       </c>
       <c r="E9" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F9" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.28902951481819</v>
+        <v>4.921967296157955</v>
       </c>
       <c r="D10" t="n">
-        <v>26.24795706578441</v>
+        <v>4.265293023189966</v>
       </c>
       <c r="E10" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F10" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.50123716796772</v>
+        <v>5.606451039794755</v>
       </c>
       <c r="D11" t="n">
-        <v>34.35415349743385</v>
+        <v>5.582549943333</v>
       </c>
       <c r="E11" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F11" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.50862543795922</v>
+        <v>7.395151633668373</v>
       </c>
       <c r="D12" t="n">
-        <v>44.27780391328873</v>
+        <v>7.195143135909419</v>
       </c>
       <c r="E12" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F12" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.15427374827181</v>
+        <v>6.525069484094169</v>
       </c>
       <c r="D13" t="n">
-        <v>40.49658060989678</v>
+        <v>6.580694349108227</v>
       </c>
       <c r="E13" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F13" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.64793808903278</v>
+        <v>2.217789939467826</v>
       </c>
       <c r="D14" t="n">
-        <v>13.98467651784753</v>
+        <v>2.272509934150223</v>
       </c>
       <c r="E14" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F14" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>4.661256827701508</v>
+        <v>0.7574542345014951</v>
       </c>
       <c r="D15" t="n">
-        <v>4.332045937767181</v>
+        <v>0.7039574648871669</v>
       </c>
       <c r="E15" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F15" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.24298522043835</v>
+        <v>7.351985098321232</v>
       </c>
       <c r="D16" t="n">
-        <v>44.90005340654045</v>
+        <v>7.296258678562824</v>
       </c>
       <c r="E16" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F16" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.75082544969369</v>
+        <v>4.997009135575225</v>
       </c>
       <c r="D17" t="n">
-        <v>31.0749048181159</v>
+        <v>5.049672032943834</v>
       </c>
       <c r="E17" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F17" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.25867188860277</v>
+        <v>2.96703418189795</v>
       </c>
       <c r="D18" t="n">
-        <v>18.32635160501285</v>
+        <v>2.978032135814589</v>
       </c>
       <c r="E18" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F18" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>49.75321665814963</v>
+        <v>8.084897706949315</v>
       </c>
       <c r="D19" t="n">
-        <v>49.99060655662001</v>
+        <v>8.123473565450752</v>
       </c>
       <c r="E19" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F19" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.55697804225038</v>
+        <v>7.728008931865687</v>
       </c>
       <c r="D20" t="n">
-        <v>47.5914413871998</v>
+        <v>7.733609225419968</v>
       </c>
       <c r="E20" t="n">
-        <v>16.33041134206209</v>
+        <v>2.65369184308509</v>
       </c>
       <c r="F20" t="n">
-        <v>13.50859258118374</v>
+        <v>2.195146294442358</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
